--- a/config_script/devices_vars.xlsx
+++ b/config_script/devices_vars.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TEMP\crt-batch-config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4_Learn\Python\securecrt_script\config_script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2AAB22-30EF-47E6-ADA0-77866F211674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9C7F0D-AEC1-4BB0-8019-3127DD2608BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-29544" yWindow="3000" windowWidth="23040" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,11 +82,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MANUFACTURER</t>
+    <t>DEVICE_NAME</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DEVICE_NAME</t>
+    <t>DEVICE_TYPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -416,7 +416,7 @@
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.53125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.53125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.53125" bestFit="1" customWidth="1"/>
@@ -428,10 +428,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
